--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,15 +1772,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1798,22 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1888,18 +1888,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2124,26 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2154,18 +2154,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2180,26 +2184,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2210,14 +2202,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2228,26 +2232,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,18 +2354,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2376,18 +2380,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,12 +2406,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2420,15 +2428,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>3</v>
@@ -2442,19 +2454,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2468,12 +2476,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2490,22 +2498,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -2516,22 +2520,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,22 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -2938,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,22 +3174,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3200,18 +3204,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3278,26 +3282,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -3308,14 +3308,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3330,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3588,18 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,7 +3618,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3622,14 +3626,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3674,18 +3674,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3715,11 +3715,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3730,22 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,12 +4304,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,22 +4326,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4352,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4374,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,12 +4396,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4414,22 +4418,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4444,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4462,22 +4466,18 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
@@ -4546,14 +4546,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -4582,22 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4612,26 +4612,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4642,22 +4634,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4672,17 +4660,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -4691,7 +4679,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4702,20 +4690,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4728,16 +4712,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4750,26 +4742,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -4780,20 +4764,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4836,18 +4816,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4858,24 +4846,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4888,16 +4868,20 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4910,17 +4894,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -4929,7 +4913,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4940,18 +4924,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4966,18 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4988,22 +4984,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5018,16 +5014,20 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,26 +5040,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5070,17 +5070,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5378,22 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,22 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5460,26 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -5490,22 +5490,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5968,26 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -5998,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6024,26 +6028,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,19 +6224,15 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
         <v>3</v>
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,22 +6268,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -6316,18 +6312,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,22 +6360,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6560,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6590,22 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6616,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6646,22 +6650,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -6896,22 +6896,18 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6926,18 +6922,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -7204,22 +7204,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7234,18 +7230,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7260,26 +7256,26 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7286,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7316,22 +7312,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,19 +7860,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7886,18 +7882,22 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -7908,22 +7908,18 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -7934,22 +7930,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7960,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7982,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8004,18 +8000,22 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -8096,18 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,18 +8126,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8148,22 +8156,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8178,18 +8186,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8204,26 +8212,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8234,18 +8238,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8260,26 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8290,26 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -8320,26 +8320,26 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,22 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8602,22 +8602,18 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8632,18 +8628,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,14 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+          <t>Core PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -8676,22 +8688,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8706,22 +8714,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8736,22 +8744,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8762,22 +8774,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8792,26 +8804,14 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -8930,22 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,22 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -9012,26 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,22 +9950,18 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -9976,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -10002,15 +9994,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10024,19 +10020,15 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>3</v>
@@ -10050,18 +10042,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10072,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10094,18 +10090,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10468,22 +10468,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -10494,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,22 +10520,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,18 +10568,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -10594,22 +10594,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,18 +11290,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11308,22 +11316,18 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11334,18 +11338,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11356,18 +11360,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -11378,18 +11386,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11400,22 +11412,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11426,22 +11434,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11452,22 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -12006,14 +12006,10 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>4.270%</t>
-        </is>
-      </c>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="n">
@@ -12028,18 +12024,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -12050,14 +12042,18 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr"/>
+          <t>42-Day Bill Auction</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>4.270%</t>
+        </is>
+      </c>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="482">
@@ -12071,7 +12067,11 @@
           <t>52-Week Bill Auction</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr"/>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="n">
@@ -12214,14 +12214,18 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr"/>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>593.6</t>
+        </is>
+      </c>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="490">
@@ -12235,7 +12239,11 @@
           <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr"/>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
@@ -12250,10 +12258,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr"/>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
@@ -12268,14 +12280,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12286,10 +12302,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
@@ -12304,18 +12324,14 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>6.93%</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12326,14 +12342,10 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>214.9</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
@@ -12348,14 +12360,10 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>593.6</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
@@ -12370,14 +12378,10 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
@@ -12392,18 +12396,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>-6.6%</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -12414,14 +12414,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12436,18 +12436,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12462,26 +12462,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12492,26 +12488,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>1.366M</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -12522,22 +12514,26 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>-9.8%</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -12548,18 +12544,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12574,14 +12570,14 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12596,22 +12592,26 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr"/>
+          <t>1.366M</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -12774,12 +12774,16 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr"/>
-      <c r="E515" t="inlineStr"/>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F515" t="n">
         <v>3</v>
       </c>
@@ -12792,22 +12796,14 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E516" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D516" t="inlineStr"/>
+      <c r="E516" t="inlineStr"/>
       <c r="F516" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="517">
@@ -12818,22 +12814,22 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F517" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
@@ -12844,7 +12840,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
@@ -12862,7 +12858,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
@@ -12880,14 +12876,18 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F520" t="n">
@@ -12902,18 +12902,18 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F521" t="n">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -13080,14 +13080,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13134,14 +13134,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,14 +13188,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13224,14 +13224,14 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
@@ -13468,22 +13468,18 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -13494,18 +13490,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F551" t="n">
@@ -13520,22 +13516,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="553">
@@ -13546,18 +13542,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -13572,18 +13568,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="555">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F555" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556">
@@ -14034,18 +14034,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14056,14 +14060,14 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F578" t="n">
@@ -14078,18 +14082,18 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F579" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="580">
@@ -14126,14 +14130,14 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -14148,14 +14152,14 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F582" t="n">
@@ -14518,14 +14522,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="600">
@@ -14536,14 +14540,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14572,7 +14576,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14644,7 +14648,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14680,7 +14684,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14698,7 +14702,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14716,14 +14720,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="611">
@@ -14824,14 +14828,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617">
@@ -14926,7 +14930,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -14944,7 +14948,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
@@ -15028,7 +15032,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -15046,7 +15050,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15136,7 +15140,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15172,7 +15176,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15460,7 +15464,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15496,7 +15500,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15514,7 +15518,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15646,7 +15650,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15738,22 +15742,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F663" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="664">
@@ -15790,18 +15794,18 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -15816,18 +15820,22 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr"/>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F666" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="667">
@@ -15838,18 +15846,14 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D667" t="inlineStr"/>
       <c r="E667" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F667" t="n">
@@ -15864,14 +15868,18 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
-      <c r="D668" t="inlineStr"/>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -15908,14 +15916,18 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
-      <c r="D670" t="inlineStr"/>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F670" t="n">
@@ -15956,22 +15968,18 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
+      <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F672" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="673">
@@ -15982,14 +15990,22 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="F673" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="674">
@@ -16222,22 +16238,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D683" t="inlineStr"/>
+      <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -16300,12 +16308,16 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr"/>
-      <c r="E686" t="inlineStr"/>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="F686" t="n">
         <v>2</v>
       </c>
@@ -16384,16 +16396,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
-      <c r="E690" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
+      <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
         <v>2</v>
       </c>
@@ -16512,7 +16520,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16578,7 +16586,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16744,7 +16752,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16762,7 +16770,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -17142,18 +17150,14 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr"/>
-      <c r="E727" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="E727" t="inlineStr"/>
       <c r="F727" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="728">
@@ -17164,22 +17168,18 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F728" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="729">
@@ -17190,14 +17190,22 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
-      <c r="D729" t="inlineStr"/>
-      <c r="E729" t="inlineStr"/>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F729" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="730">
@@ -17208,16 +17216,12 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr"/>
-      <c r="E730" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E730" t="inlineStr"/>
       <c r="F730" t="n">
         <v>1</v>
       </c>
@@ -17230,14 +17234,18 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr"/>
-      <c r="E731" t="inlineStr"/>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F731" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="732">
@@ -17248,7 +17256,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17266,7 +17274,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -17284,7 +17292,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F779"/>
+  <dimension ref="A1:F789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,18 +1798,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1824,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1888,15 +1884,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -2124,26 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2154,26 +2154,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2184,14 +2172,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2202,22 +2198,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>201K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>218K</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>213K</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2228,22 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,18 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,19 +2402,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2424,18 +2424,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,22 +2450,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2472,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,15 +2516,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>3</v>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/09</t>
+          <t>15-Year Mortgage RateJAN/09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2810,12 +2810,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/09</t>
+          <t>30-Year Mortgage RateJAN/09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2886,26 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,26 +3226,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3256,22 +3252,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3293,7 +3293,7 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,10 +3330,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3348,12 +3352,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3370,14 +3374,10 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3566,14 +3566,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,18 +3584,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3629,11 +3629,11 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3644,26 +3644,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,22 +3674,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,22 +3700,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3734,22 +3730,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3970,18 +3970,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,18 +4014,18 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,22 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4322,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,18 +4370,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4392,18 +4396,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,19 +4422,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4440,12 +4444,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4462,22 +4466,18 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,18 +4604,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4660,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4698,26 +4690,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4728,18 +4712,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4754,12 +4742,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4776,26 +4764,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4806,26 +4786,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4836,18 +4816,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4858,12 +4846,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4880,22 +4868,18 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -4910,18 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4954,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4988,18 +4980,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5010,22 +5010,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5266,22 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.499M</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5296,18 +5296,18 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5322,22 +5322,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,22 +6246,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,22 +6408,18 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -6590,22 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>4.24M</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6616,22 +6620,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6646,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6676,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7204,22 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -7230,18 +7234,22 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7256,22 +7264,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7286,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7312,26 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7816,19 +7816,15 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
         <v>3</v>
@@ -7842,22 +7838,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7868,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7890,12 +7882,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7912,22 +7904,22 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -7938,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7960,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7982,18 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8004,18 +8000,22 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -8096,18 +8096,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -8152,26 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8182,22 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8234,26 +8238,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,26 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -8294,26 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -8324,18 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,22 +9972,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10046,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,22 +10068,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,12 +10116,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10468,22 +10468,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10494,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,18 +10520,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10542,18 +10546,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,18 +10572,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10598,14 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,18 +10880,18 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10906,18 +10906,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -10928,14 +10932,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10950,22 +10954,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10976,22 +10976,18 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -11002,14 +10998,18 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11024,22 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -11050,14 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11072,14 +11072,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11094,22 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -11478,22 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -11504,18 +11500,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11530,18 +11526,14 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -11556,18 +11548,22 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -11578,14 +11574,18 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F459" t="n">
@@ -11819,11 +11819,7 @@
           <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
+      <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
           <t>47</t>
@@ -11849,7 +11845,11 @@
           <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr"/>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="D471" t="inlineStr">
         <is>
           <t>47</t>
@@ -12089,11 +12089,7 @@
           <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>$87.1B</t>
-        </is>
-      </c>
+      <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr"/>
       <c r="F483" t="n">
@@ -12111,11 +12107,7 @@
           <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>$-49.7B</t>
-        </is>
-      </c>
+      <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="n">
@@ -12133,11 +12125,7 @@
           <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>$72B</t>
-        </is>
-      </c>
+      <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr">
         <is>
           <t>$149.1B</t>
@@ -12159,7 +12147,11 @@
           <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr"/>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>$-49.7B</t>
+        </is>
+      </c>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="n">
@@ -12174,14 +12166,22 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr"/>
-      <c r="D487" t="inlineStr"/>
+          <t>Net Long-term TIC FlowsDEC</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>$72B</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -12192,18 +12192,18 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+          <t>Overall Net Capital FlowsDEC</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>$87.1B</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="489">
@@ -12304,18 +12304,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr"/>
@@ -12348,12 +12348,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="D496" t="inlineStr"/>
@@ -12370,12 +12370,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D497" t="inlineStr"/>
@@ -12392,18 +12392,18 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -12417,11 +12417,7 @@
           <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
@@ -12440,22 +12436,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -12466,22 +12458,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>Housing Starts MoMJAN</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12492,22 +12484,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>1.366M</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12522,18 +12514,26 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
+          <t>Housing StartsJAN</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>1.366M</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -12547,11 +12547,7 @@
           <t>Building Permits PrelJAN</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
           <t>1.46M</t>
@@ -12574,18 +12570,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12600,18 +12596,22 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -12774,18 +12774,14 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+      <c r="D515" t="inlineStr"/>
       <c r="E515" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F515" t="n">
@@ -12800,7 +12796,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
@@ -12818,22 +12814,14 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="inlineStr"/>
       <c r="F517" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="518">
@@ -12844,22 +12832,14 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr"/>
       <c r="F518" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="519">
@@ -12870,14 +12850,22 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
-      <c r="D519" t="inlineStr"/>
-      <c r="E519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F519" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="520">
@@ -12888,14 +12876,22 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr"/>
-      <c r="E520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F520" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="521">
@@ -12906,16 +12902,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr"/>
-      <c r="E521" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E521" t="inlineStr"/>
       <c r="F521" t="n">
         <v>3</v>
       </c>
@@ -12928,7 +12920,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -12946,12 +12938,20 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
-      <c r="D523" t="inlineStr"/>
-      <c r="E523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F523" t="n">
         <v>3</v>
       </c>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -13080,14 +13080,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -13098,14 +13098,14 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,14 +13188,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13224,14 +13224,14 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13368,18 +13368,18 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F546" t="n">
@@ -13394,11 +13394,15 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -13416,18 +13420,14 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F548" t="n">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13798,7 +13798,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13942,22 +13942,18 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F573" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="574">
@@ -13968,14 +13964,14 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F574" t="n">
@@ -13990,14 +13986,18 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F575" t="n">
@@ -14012,14 +14012,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -14034,18 +14034,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14056,22 +14060,22 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F578" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="579">
@@ -14082,14 +14086,18 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -14104,22 +14112,18 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F580" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="581">
@@ -14130,18 +14134,14 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -14156,14 +14156,14 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F582" t="n">
@@ -14178,14 +14178,14 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F583" t="n">
@@ -14200,22 +14200,22 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F584" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="585">
@@ -14226,22 +14226,22 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F585" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="586">
@@ -14274,22 +14274,22 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F587" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="588">
@@ -14300,22 +14300,22 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F588" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="589">
@@ -14326,14 +14326,14 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14512,7 +14512,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
@@ -14530,14 +14530,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -14548,14 +14548,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14566,14 +14566,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14584,14 +14584,14 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14674,7 +14674,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14692,14 +14692,14 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="609">
@@ -14710,14 +14710,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14746,14 +14746,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14836,14 +14836,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="617">
@@ -14890,14 +14890,18 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>0.69M</t>
+        </is>
+      </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="F619" t="n">
@@ -14912,18 +14916,14 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
-      <c r="D620" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
+      <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F620" t="n">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
@@ -14974,14 +14974,18 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>0.69M</t>
+        </is>
+      </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="F623" t="n">
@@ -14996,18 +15000,14 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
-      <c r="D624" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
+      <c r="D624" t="inlineStr"/>
       <c r="E624" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F624" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -15058,14 +15058,14 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr"/>
       <c r="E627" t="inlineStr"/>
       <c r="F627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -15076,14 +15076,14 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr"/>
       <c r="E628" t="inlineStr"/>
       <c r="F628" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="629">
@@ -15112,14 +15112,14 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
       <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr"/>
       <c r="F630" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="631">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15202,14 +15202,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15238,14 +15238,14 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr"/>
       <c r="F637" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="638">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
@@ -15274,14 +15274,14 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15346,14 +15346,14 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr"/>
       <c r="F643" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -15364,14 +15364,14 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr"/>
       <c r="F644" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="645">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15548,20 +15548,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E654" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D654" t="inlineStr"/>
+      <c r="E654" t="inlineStr"/>
       <c r="F654" t="n">
         <v>3</v>
       </c>
@@ -15574,7 +15566,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15592,16 +15584,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr"/>
-      <c r="E656" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E656" t="inlineStr"/>
       <c r="F656" t="n">
         <v>3</v>
       </c>
@@ -15640,12 +15628,16 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr"/>
-      <c r="E658" t="inlineStr"/>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F658" t="n">
         <v>3</v>
       </c>
@@ -15658,12 +15650,20 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
-      <c r="D659" t="inlineStr"/>
-      <c r="E659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="F659" t="n">
         <v>3</v>
       </c>
@@ -15676,22 +15676,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F660" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="661">
@@ -15702,14 +15702,18 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
-      <c r="D661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -15724,22 +15728,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F662" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="663">
@@ -15794,18 +15798,18 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -15820,18 +15824,14 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D666" t="inlineStr"/>
       <c r="E666" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -15846,18 +15846,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr"/>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F667" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="668">
@@ -15868,22 +15872,18 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
-      <c r="D668" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D668" t="inlineStr"/>
       <c r="E668" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F668" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="669">
@@ -15894,22 +15894,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F669" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="670">
@@ -15920,18 +15920,18 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F670" t="n">
@@ -15946,22 +15946,18 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
-      <c r="D671" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D671" t="inlineStr"/>
       <c r="E671" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F671" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="672">
@@ -15972,18 +15968,22 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F672" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="673">
@@ -15994,22 +15994,22 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F673" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="674">
@@ -16020,22 +16020,22 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F674" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
@@ -16046,18 +16046,22 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr"/>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F675" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="676">
@@ -16068,18 +16072,18 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -16094,22 +16098,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F677" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678">
@@ -16120,18 +16124,18 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -16146,22 +16150,22 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -16172,18 +16176,14 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F680" t="n">
@@ -16198,22 +16198,22 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F681" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -16224,18 +16224,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
-      <c r="D682" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -16250,14 +16246,18 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F683" t="n">
@@ -16272,22 +16272,18 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F684" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">
@@ -16298,14 +16294,18 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -16386,12 +16386,20 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
-      <c r="D689" t="inlineStr"/>
-      <c r="E689" t="inlineStr"/>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="F689" t="n">
         <v>2</v>
       </c>
@@ -16426,20 +16434,12 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E691" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D691" t="inlineStr"/>
+      <c r="E691" t="inlineStr"/>
       <c r="F691" t="n">
         <v>2</v>
       </c>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -16944,18 +16944,22 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F718" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="719">
@@ -16966,22 +16970,22 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F719" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="720">
@@ -16992,22 +16996,18 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr">
+      <c r="D720" t="inlineStr"/>
+      <c r="E720" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E720" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F720" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="721">
@@ -17018,22 +17018,18 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
-      <c r="D721" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F721" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="722">
@@ -17044,18 +17040,14 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>$-114.7B</t>
-        </is>
-      </c>
+      <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F722" t="n">
@@ -17070,14 +17062,18 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr"/>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F723" t="n">
@@ -17092,18 +17088,18 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F724" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="725">
@@ -17114,18 +17110,18 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F725" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="726">
@@ -17136,14 +17132,18 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
-      <c r="D726" t="inlineStr"/>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F726" t="n">
@@ -17158,18 +17158,22 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr"/>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F727" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="728">
@@ -17180,22 +17184,22 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F728" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="729">
@@ -17206,22 +17210,22 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F729" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="730">
@@ -17232,22 +17236,18 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
-      <c r="D730" t="inlineStr">
+      <c r="D730" t="inlineStr"/>
+      <c r="E730" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E730" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F730" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="731">
@@ -17258,22 +17258,22 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F731" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="732">
@@ -17310,18 +17310,18 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F733" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="734">
@@ -17354,22 +17354,22 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F735" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="736">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17556,18 +17556,18 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F744" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="745">
@@ -17600,18 +17600,18 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="747">
@@ -17688,18 +17688,18 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
       <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F750" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="751">
@@ -17710,18 +17710,18 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F751" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="752">
@@ -17732,14 +17732,14 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="F752" t="n">
@@ -17754,14 +17754,14 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F753" t="n">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -17830,7 +17830,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
@@ -17928,15 +17928,11 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr"/>
       <c r="F762" t="n">
         <v>3</v>
@@ -17950,15 +17946,11 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
         <v>3</v>
@@ -17972,11 +17964,15 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
         <v>3</v>
@@ -17990,11 +17986,15 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
         <v>3</v>
@@ -18044,7 +18044,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -18134,14 +18134,14 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr"/>
       <c r="E773" t="inlineStr"/>
       <c r="F773" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="774">
@@ -18152,14 +18152,14 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
       <c r="D774" t="inlineStr"/>
       <c r="E774" t="inlineStr"/>
       <c r="F774" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="775">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
@@ -18188,7 +18188,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
@@ -18206,7 +18206,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -18260,6 +18260,222 @@
         <v>2</v>
       </c>
     </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:15:00+05:30</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Composite PMI FinalFEB</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr"/>
+      <c r="D780" t="inlineStr"/>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:15:00+05:30</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="F781" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>ISM Services PMIFEB</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr"/>
+      <c r="D782" t="inlineStr"/>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="F782" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Factory Orders MoMJAN</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr"/>
+      <c r="D783" t="inlineStr"/>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F783" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Factory Orders ex TransportationJAN</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr"/>
+      <c r="D784" t="inlineStr"/>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F784" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>ISM Services Business ActivityFEB</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr"/>
+      <c r="D785" t="inlineStr"/>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="F785" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>ISM Services EmploymentFEB</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr"/>
+      <c r="D786" t="inlineStr"/>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="F786" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>ISM Services New OrdersFEB</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr"/>
+      <c r="D787" t="inlineStr"/>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>51.2</t>
+        </is>
+      </c>
+      <c r="F787" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>ISM Services PricesFEB</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr"/>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="F788" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Total Vehicle SalesFEB</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr"/>
+      <c r="D789" t="inlineStr"/>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F789"/>
+  <dimension ref="A1:F809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,22 +790,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -816,15 +812,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,17 +838,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -864,19 +864,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -890,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -912,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,18 +930,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1088,26 +1088,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1118,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1144,26 +1148,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1174,26 +1174,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1424,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1450,26 +1454,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,22 +1802,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1824,22 +1832,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,26 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2154,12 +2154,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+          <t>Initial Jobless ClaimsJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>201K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>218K</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="F71" t="n">
         <v>2</v>
       </c>
@@ -2172,18 +2184,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2198,24 +2214,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
         <v>2</v>
       </c>
@@ -2228,22 +2232,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,22 +2376,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2402,15 +2398,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2450,18 +2450,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2472,12 +2476,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2494,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2516,19 +2520,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>3</v>
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2968,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3308,14 +3308,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3330,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3352,12 +3348,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3374,10 +3370,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
@@ -3558,18 +3558,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -3614,26 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3644,22 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,18 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3700,7 +3704,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3708,14 +3712,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3745,11 +3745,11 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,18 +3970,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,19 +4300,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,12 +4322,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4348,18 +4344,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4370,22 +4370,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4396,22 +4392,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4422,12 +4414,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4444,15 +4436,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4466,18 +4462,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,18 +4612,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4630,22 +4638,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4660,17 +4668,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -4679,7 +4687,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4690,16 +4698,20 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4712,24 +4724,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4742,18 +4746,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -4764,18 +4776,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4786,22 +4806,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4816,26 +4836,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4846,16 +4858,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,20 +4888,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4894,17 +4910,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -4913,7 +4929,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4940,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4954,18 +4970,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4980,26 +4996,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5010,24 +5018,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5378,22 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -5438,22 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5464,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5490,22 +5494,18 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5740,18 +5740,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5784,12 +5784,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5806,18 +5806,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -6080,18 +6080,18 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexJAN</t>
+          <t>Kansas Fed Composite IndexJAN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -6106,18 +6106,18 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexJAN</t>
+          <t>Kansas Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6766,12 +6766,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/24</t>
+          <t>Baker Hughes Oil Rig CountJAN/24</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -6788,12 +6788,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/24</t>
+          <t>Baker Hughes Total Rigs CountJAN/24</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>576</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7156,22 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7760,18 +7760,22 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -7786,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -7816,18 +7816,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -7838,12 +7842,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7904,19 +7908,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7930,15 +7930,19 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>3</v>
@@ -7952,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7974,22 +7978,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8572,18 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8602,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8628,22 +8632,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,20 +8662,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
         <v>2</v>
       </c>
@@ -8684,22 +8680,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8714,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8744,12 +8740,20 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8762,26 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -8930,22 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8986,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9012,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9046,22 +9042,26 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,19 +9976,15 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>3</v>
@@ -9998,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,22 +10020,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10046,15 +10042,19 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10068,22 +10068,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10094,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,18 +10112,22 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -10468,22 +10468,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -10494,22 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -10520,18 +10516,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,18 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10598,14 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,22 +10880,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -10906,22 +10906,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -10932,14 +10932,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10954,14 +10954,14 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10976,14 +10976,18 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,18 +11002,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11024,22 +11024,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11046,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11072,14 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11094,22 +11098,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,14 +11290,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F447" t="n">
@@ -11308,18 +11312,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -11330,18 +11338,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F449" t="n">
@@ -11356,22 +11360,18 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -11382,14 +11382,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -11404,22 +11408,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11430,22 +11430,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11456,14 +11456,14 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11763,7 +11763,11 @@
           <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr"/>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
       <c r="D468" t="inlineStr">
         <is>
           <t>-1</t>
@@ -11789,11 +11793,7 @@
           <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
+      <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
           <t>-1</t>
@@ -12089,7 +12089,11 @@
           <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr"/>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>$87.1B</t>
+        </is>
+      </c>
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr"/>
       <c r="F483" t="n">
@@ -12104,14 +12108,22 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr"/>
-      <c r="D484" t="inlineStr"/>
+          <t>Net Long-term TIC FlowsDEC</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>$72B</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="485">
@@ -12122,18 +12134,18 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+          <t>Foreign Bond InvestmentDEC</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>$-49.7B</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="486">
@@ -12144,18 +12156,18 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>$-49.7B</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr"/>
+          <t>Net Long-term TIC FlowsDEC</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487">
@@ -12166,22 +12178,14 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>$72B</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+          <t>Overall Net Capital FlowsDEC</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -12192,14 +12196,10 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>$87.1B</t>
-        </is>
-      </c>
+          <t>Foreign Bond InvestmentDEC</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="n">
@@ -12414,18 +12414,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -12436,14 +12440,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr"/>
+          <t>Building Permits MoM PrelJAN</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12458,22 +12466,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>-9.8%</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr"/>
+          <t>Building Permits PrelJAN</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
@@ -12484,22 +12492,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.366M</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12514,26 +12522,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>1.366M</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>Housing Starts MoMJAN</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -12544,22 +12544,22 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>Housing Starts MoMJAN</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -12573,11 +12573,7 @@
           <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
@@ -12596,18 +12592,22 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr"/>
+          <t>Building Permits PrelJAN</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F506" t="n">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
@@ -13044,7 +13044,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
@@ -13942,18 +13942,22 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F573" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -13964,14 +13968,14 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F574" t="n">
@@ -14012,14 +14016,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -14034,22 +14038,18 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
@@ -14060,22 +14060,22 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F578" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="579">
@@ -14086,18 +14086,14 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -14112,14 +14108,14 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F580" t="n">
@@ -14156,18 +14152,22 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F582" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="583">
@@ -14200,22 +14200,18 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
+      <c r="D584" t="inlineStr"/>
       <c r="E584" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F584" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585">
@@ -14252,18 +14248,22 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
+      </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F586" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="587">
@@ -14274,22 +14274,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F587" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="588">
@@ -14300,18 +14296,14 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+      <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -14326,14 +14318,18 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14348,18 +14344,22 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F590" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="591">
@@ -14392,14 +14392,14 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -14436,14 +14436,14 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -14494,14 +14494,14 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
@@ -14530,14 +14530,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="600">
@@ -14548,14 +14548,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14566,14 +14566,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14674,7 +14674,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14692,14 +14692,14 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="609">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14746,14 +14746,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="612">
@@ -14764,14 +14764,14 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="613">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14836,14 +14836,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617">
@@ -14890,20 +14890,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
-      <c r="E619" t="inlineStr">
-        <is>
-          <t>0.68M</t>
-        </is>
-      </c>
+      <c r="D619" t="inlineStr"/>
+      <c r="E619" t="inlineStr"/>
       <c r="F619" t="n">
         <v>2</v>
       </c>
@@ -14916,14 +14908,18 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>0.69M</t>
+        </is>
+      </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="F620" t="n">
@@ -14938,12 +14934,16 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr"/>
-      <c r="E621" t="inlineStr"/>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
       <c r="F621" t="n">
         <v>2</v>
       </c>
@@ -14956,12 +14956,16 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr"/>
-      <c r="E622" t="inlineStr"/>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
       <c r="F622" t="n">
         <v>2</v>
       </c>
@@ -15000,16 +15004,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr"/>
-      <c r="E624" t="inlineStr">
-        <is>
-          <t>-2.6%</t>
-        </is>
-      </c>
+      <c r="E624" t="inlineStr"/>
       <c r="F624" t="n">
         <v>2</v>
       </c>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15202,14 +15202,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -15256,14 +15256,14 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr"/>
       <c r="F638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15346,14 +15346,14 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr"/>
       <c r="F643" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644">
@@ -15364,14 +15364,14 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr"/>
       <c r="F644" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
@@ -15526,14 +15526,18 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="F653" t="n">
@@ -15566,12 +15570,20 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
-      <c r="D655" t="inlineStr"/>
-      <c r="E655" t="inlineStr"/>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="F655" t="n">
         <v>3</v>
       </c>
@@ -15584,12 +15596,16 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr"/>
-      <c r="E656" t="inlineStr"/>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F656" t="n">
         <v>3</v>
       </c>
@@ -15602,20 +15618,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E657" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D657" t="inlineStr"/>
+      <c r="E657" t="inlineStr"/>
       <c r="F657" t="n">
         <v>3</v>
       </c>
@@ -15628,16 +15636,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr"/>
-      <c r="E658" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E658" t="inlineStr"/>
       <c r="F658" t="n">
         <v>3</v>
       </c>
@@ -15650,18 +15654,14 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
-      <c r="D659" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F659" t="n">
@@ -15676,22 +15676,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F660" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="661">
@@ -15702,18 +15702,18 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -15728,22 +15728,18 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr">
+      <c r="D662" t="inlineStr"/>
+      <c r="E662" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E662" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F662" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="663">
@@ -15754,14 +15750,18 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
-      <c r="D663" t="inlineStr"/>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F663" t="n">
@@ -15776,14 +15776,18 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
-      <c r="D664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -15798,18 +15802,14 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -15824,18 +15824,22 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr"/>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F666" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="667">
@@ -15846,18 +15850,18 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F667" t="n">
@@ -15872,18 +15876,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
-      <c r="D668" t="inlineStr"/>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F668" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="669">
@@ -15894,22 +15902,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F669" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670">
@@ -15920,22 +15928,22 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F670" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="671">
@@ -15946,14 +15954,14 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr"/>
       <c r="E671" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F671" t="n">
@@ -15968,22 +15976,18 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F672" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="673">
@@ -15994,18 +15998,14 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F673" t="n">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -16035,7 +16035,7 @@
         </is>
       </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="675">
@@ -16046,22 +16046,22 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F675" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -16072,18 +16072,18 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -16224,14 +16224,18 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
-      <c r="D682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -16246,18 +16250,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F683" t="n">
@@ -16272,14 +16272,18 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F684" t="n">
@@ -16294,18 +16298,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -16320,12 +16320,20 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
-      <c r="D686" t="inlineStr"/>
-      <c r="E686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
       <c r="F686" t="n">
         <v>2</v>
       </c>
@@ -16360,18 +16368,14 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
+      <c r="D688" t="inlineStr"/>
       <c r="E688" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F688" t="n">
@@ -16386,20 +16390,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
-      <c r="D689" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E689" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D689" t="inlineStr"/>
+      <c r="E689" t="inlineStr"/>
       <c r="F689" t="n">
         <v>2</v>
       </c>
@@ -16412,14 +16408,18 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
-      <c r="D690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F690" t="n">
@@ -16492,11 +16492,15 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="n">
         <v>3</v>
@@ -16510,15 +16514,11 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D695" t="inlineStr"/>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="n">
         <v>3</v>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16944,22 +16944,18 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F718" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="719">
@@ -16970,18 +16966,18 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F719" t="n">
@@ -17018,14 +17014,14 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F721" t="n">
@@ -17040,14 +17036,18 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr"/>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F722" t="n">
@@ -17062,22 +17062,22 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F723" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
@@ -17088,18 +17088,22 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
-      <c r="D724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F724" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="725">
@@ -17110,18 +17114,22 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
-      <c r="D725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F725" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="726">
@@ -17132,18 +17140,14 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
-      <c r="D726" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F726" t="n">
@@ -17158,22 +17162,18 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F727" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="728">
@@ -17184,18 +17184,18 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E728" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F728" t="n">
@@ -17210,18 +17210,18 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F729" t="n">
@@ -17236,14 +17236,18 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
-      <c r="D730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F730" t="n">
@@ -17258,18 +17262,14 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
-      <c r="D731" t="inlineStr">
-        <is>
-          <t>$-114.7B</t>
-        </is>
-      </c>
+      <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F731" t="n">
@@ -17284,18 +17284,18 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
       <c r="D732" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E732" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F732" t="n">
@@ -17310,18 +17310,18 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F733" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="734">
@@ -17332,18 +17332,18 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F734" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="735">
@@ -17354,22 +17354,22 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F735" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="736">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -17556,18 +17556,18 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F744" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="745">
@@ -17578,18 +17578,18 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr"/>
       <c r="E745" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="F745" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="746">
@@ -17600,14 +17600,14 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F746" t="n">
@@ -17622,14 +17622,14 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="F747" t="n">
@@ -17644,18 +17644,18 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F748" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="749">
@@ -17666,18 +17666,18 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F749" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="750">
@@ -17688,18 +17688,18 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
       <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F750" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="751">
@@ -17710,18 +17710,18 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F751" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="752">
@@ -17732,18 +17732,18 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F752" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="753">
@@ -17754,14 +17754,14 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F753" t="n">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -17812,7 +17812,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
@@ -17946,11 +17946,15 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
         <v>3</v>
@@ -17964,15 +17968,11 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
         <v>3</v>
@@ -18044,7 +18044,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
@@ -18062,14 +18062,14 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
       <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr"/>
       <c r="F769" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="770">
@@ -18098,14 +18098,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr"/>
       <c r="F771" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="772">
@@ -18134,7 +18134,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
@@ -18152,14 +18152,14 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
       <c r="D774" t="inlineStr"/>
       <c r="E774" t="inlineStr"/>
       <c r="F774" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="775">
@@ -18170,14 +18170,14 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
       <c r="D775" t="inlineStr"/>
       <c r="E775" t="inlineStr"/>
       <c r="F775" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="776">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -18286,20 +18286,12 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalFEB</t>
+          <t>S&amp;P Global Composite PMI FinalFEB</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="E781" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+      <c r="D781" t="inlineStr"/>
+      <c r="E781" t="inlineStr"/>
       <c r="F781" t="n">
         <v>2</v>
       </c>
@@ -18307,41 +18299,49 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
-      <c r="D782" t="inlineStr"/>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="F782" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2025-03-05 20:30:00+05:30</t>
+          <t>2025-03-05 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
-      <c r="D783" t="inlineStr"/>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="F783" t="n">
@@ -18356,14 +18356,14 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
       <c r="D784" t="inlineStr"/>
       <c r="E784" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="F784" t="n">
@@ -18378,14 +18378,14 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
       <c r="D785" t="inlineStr"/>
       <c r="E785" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="F785" t="n">
@@ -18422,14 +18422,14 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C787" t="inlineStr"/>
       <c r="D787" t="inlineStr"/>
       <c r="E787" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F787" t="n">
@@ -18444,14 +18444,14 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
       <c r="D788" t="inlineStr"/>
       <c r="E788" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F788" t="n">
@@ -18466,13 +18466,409 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr"/>
-      <c r="E789" t="inlineStr"/>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
       <c r="F789" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>ISM Services PMIFEB</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr"/>
+      <c r="D790" t="inlineStr"/>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="F790" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>ISM Services PMIFEB</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr"/>
+      <c r="D791" t="inlineStr"/>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="F791" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Total Vehicle SalesFEB</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr"/>
+      <c r="D792" t="inlineStr"/>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>ISM Services PricesFEB</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr"/>
+      <c r="D793" t="inlineStr"/>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="F793" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>ISM Services New OrdersFEB</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr"/>
+      <c r="D794" t="inlineStr"/>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>51.2</t>
+        </is>
+      </c>
+      <c r="F794" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>ISM Services EmploymentFEB</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr"/>
+      <c r="D795" t="inlineStr"/>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="F795" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>ISM Services Business ActivityFEB</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr"/>
+      <c r="D796" t="inlineStr"/>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="F796" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Factory Orders ex TransportationJAN</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr"/>
+      <c r="D797" t="inlineStr"/>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F797" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2025-03-05 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Factory Orders MoMJAN</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr"/>
+      <c r="D798" t="inlineStr"/>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F798" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr"/>
+      <c r="D799" t="inlineStr"/>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr"/>
+      <c r="D800" t="inlineStr"/>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr"/>
+      <c r="D801" t="inlineStr"/>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr"/>
+      <c r="D802" t="inlineStr"/>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr"/>
+      <c r="D803" t="inlineStr"/>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr"/>
+      <c r="D804" t="inlineStr"/>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr"/>
+      <c r="D805" t="inlineStr"/>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr"/>
+      <c r="D806" t="inlineStr"/>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr"/>
+      <c r="D807" t="inlineStr"/>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2025-03-05 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>17-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr"/>
+      <c r="D808" t="inlineStr"/>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2025-03-05 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Total Vehicle SalesFEB</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr"/>
+      <c r="D809" t="inlineStr"/>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F809"/>
+  <dimension ref="A1:F820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,12 +794,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -812,19 +816,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,22 +838,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -864,15 +860,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1088,26 +1088,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1118,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,22 +1144,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1174,26 +1174,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1424,26 +1424,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1454,22 +1450,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1712,26 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1742,22 +1738,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1768,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1794,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,18 +1824,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,22 +1854,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2124,22 +2124,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2154,24 +2150,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
         <v>2</v>
       </c>
@@ -2184,22 +2168,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2214,12 +2198,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>Initial Jobless ClaimsJAN/04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>201K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>218K</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="F73" t="n">
         <v>2</v>
       </c>
@@ -2232,18 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2332,18 +2332,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2354,12 +2358,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,12 +2380,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2398,19 +2402,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2450,22 +2450,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2476,12 +2472,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2498,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,15 +2516,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>3</v>
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,10 +3308,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,12 +3330,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,18 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3584,12 +3588,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3599,11 +3603,11 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3614,22 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,7 +3648,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3652,14 +3656,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,18 +3704,18 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,26 +3730,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,18 +4014,18 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4322,18 +4326,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4344,22 +4352,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4370,12 +4374,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,18 +4396,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,12 +4422,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4436,19 +4444,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4462,22 +4466,18 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,20 +4604,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4638,22 +4626,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -4668,17 +4656,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -4687,7 +4675,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4698,20 +4686,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4724,16 +4708,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4746,26 +4738,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -4776,22 +4760,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -4806,26 +4790,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4836,18 +4816,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4858,24 +4846,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4888,16 +4868,20 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4910,17 +4894,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -4929,7 +4913,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4940,22 +4924,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4970,18 +4954,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4996,18 +4980,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5018,18 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/16</t>
+          <t>15-Year Mortgage RateJAN/16</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/16</t>
+          <t>30-Year Mortgage RateJAN/16</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>7.04%</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
+          <t>$159.9B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -6176,22 +6176,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6202,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6224,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,22 +6242,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6272,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6294,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,22 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,18 +6382,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6560,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6590,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6620,22 +6616,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,12 +6646,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6680,22 +6676,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>4.24M</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -7204,26 +7204,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -7234,22 +7230,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7264,22 +7256,26 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7286,22 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7316,18 +7316,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -7528,12 +7528,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -7816,17 +7816,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -7842,12 +7842,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7864,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,15 +7886,19 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7908,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,19 +7934,15 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>3</v>
@@ -7956,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,18 +7978,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8000,22 +8004,18 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -8096,22 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -8122,22 +8126,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,26 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8182,26 +8182,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8212,22 +8208,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8238,18 +8238,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8264,26 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -8324,18 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,22 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8602,26 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8632,26 +8628,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8662,14 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+          <t>Personal Spending MoMDEC</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8680,22 +8684,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8710,26 +8714,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8740,22 +8744,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -8766,18 +8774,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8792,24 +8804,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,18 +9498,18 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -9542,18 +9542,18 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="368">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,18 +9794,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9820,18 +9820,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,18 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,15 +9950,19 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>3</v>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,22 +10042,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -10468,18 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10494,18 +10494,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10516,22 +10520,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10542,22 +10546,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -10568,18 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,22 +10594,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,22 +10880,18 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="429">
@@ -10906,22 +10902,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
@@ -10932,18 +10928,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -10954,14 +10954,14 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10976,18 +10976,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -11002,14 +10998,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11024,14 +11020,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,22 +11046,18 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11072,22 +11068,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -11098,18 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,22 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -11290,14 +11286,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
@@ -11312,22 +11308,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11338,14 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
@@ -11360,18 +11360,18 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -11382,22 +11382,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -11408,14 +11408,14 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11430,13 +11430,13 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -11456,14 +11456,14 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -12006,10 +12006,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr"/>
+          <t>42-Day Bill Auction</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>4.270%</t>
+        </is>
+      </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="n">
@@ -12024,14 +12028,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr"/>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12042,14 +12050,10 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>4.270%</t>
-        </is>
-      </c>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="n">
@@ -12064,18 +12068,14 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483">
@@ -12214,14 +12214,18 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -12235,7 +12239,11 @@
           <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr"/>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>593.6</t>
+        </is>
+      </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
@@ -12250,14 +12258,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr"/>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-6.6%</t>
+        </is>
+      </c>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -12268,10 +12280,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr"/>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
@@ -12289,7 +12305,11 @@
           <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr"/>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>214.9</t>
+        </is>
+      </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
@@ -12304,14 +12324,10 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
@@ -12326,18 +12342,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>-6.6%</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12348,14 +12360,10 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>214.9</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
@@ -12370,14 +12378,10 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>593.6</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
@@ -12392,18 +12396,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>6.93%</t>
-        </is>
-      </c>
+          <t>MBA Mortgage Market IndexFEB/14</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -12414,18 +12414,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr"/>
+          <t>Building Permits PrelJAN</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12443,11 +12447,7 @@
           <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
@@ -12466,22 +12466,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>Housing Starts MoMJAN</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12492,26 +12492,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>1.366M</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+          <t>Housing Starts MoMJAN</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -12522,18 +12514,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -12544,18 +12540,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12570,18 +12566,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -12592,22 +12592,22 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.366M</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F506" t="n">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13116,14 +13116,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13206,14 +13206,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13368,18 +13368,14 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F546" t="n">
@@ -13394,18 +13390,18 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F547" t="n">
@@ -13420,11 +13416,15 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13798,7 +13798,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13942,22 +13942,18 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F573" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="574">
@@ -13968,14 +13964,18 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F574" t="n">
@@ -13990,18 +13990,14 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F575" t="n">
@@ -14016,14 +14012,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -14038,18 +14034,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14060,22 +14060,22 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F578" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="579">
@@ -14086,14 +14086,18 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -14108,14 +14112,14 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F580" t="n">
@@ -14152,22 +14156,18 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F582" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="583">
@@ -14274,18 +14274,22 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>102.1</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F587" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="588">
@@ -14296,14 +14300,18 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -14318,18 +14326,14 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+      <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14344,22 +14348,18 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
+      <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F590" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="591">
@@ -14392,14 +14392,14 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -14414,14 +14414,14 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr"/>
       <c r="E593" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F593" t="n">
@@ -14548,14 +14548,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14566,14 +14566,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14710,14 +14710,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="610">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14764,14 +14764,14 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613">
@@ -14890,12 +14890,16 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr"/>
-      <c r="E619" t="inlineStr"/>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
       <c r="F619" t="n">
         <v>2</v>
       </c>
@@ -14934,16 +14938,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr"/>
-      <c r="E621" t="inlineStr">
-        <is>
-          <t>-2.6%</t>
-        </is>
-      </c>
+      <c r="E621" t="inlineStr"/>
       <c r="F621" t="n">
         <v>2</v>
       </c>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -15256,14 +15256,14 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr"/>
       <c r="F638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -15328,14 +15328,14 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr"/>
       <c r="F642" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="643">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15526,20 +15526,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+      <c r="D653" t="inlineStr"/>
+      <c r="E653" t="inlineStr"/>
       <c r="F653" t="n">
         <v>3</v>
       </c>
@@ -15618,12 +15610,20 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr"/>
-      <c r="E657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="F657" t="n">
         <v>3</v>
       </c>
@@ -15676,18 +15676,18 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F660" t="n">
@@ -15702,18 +15702,14 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
-      <c r="D661" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -15728,14 +15724,14 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F662" t="n">
@@ -15776,18 +15772,14 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
-      <c r="D664" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -15802,18 +15794,22 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr"/>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F665" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="666">
@@ -15824,18 +15820,18 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -15850,22 +15846,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F667" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="668">
@@ -15954,14 +15950,18 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
-      <c r="D671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F671" t="n">
@@ -15976,14 +15976,14 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F672" t="n">
@@ -15998,14 +15998,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F673" t="n">
@@ -16020,18 +16024,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F674" t="n">
@@ -16046,18 +16050,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -16072,22 +16072,22 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F676" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="677">
@@ -16098,22 +16098,18 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
-      <c r="D677" t="inlineStr">
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F677" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="678">
@@ -16124,22 +16120,22 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F678" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="679">
@@ -16150,22 +16146,18 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
-      <c r="D679" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+      <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="F679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680">
@@ -16176,18 +16168,22 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="F680" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681">
@@ -16198,22 +16194,22 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -16224,18 +16220,18 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -16250,18 +16246,22 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -16272,18 +16272,14 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F684" t="n">
@@ -16298,18 +16294,22 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="686">
@@ -16320,20 +16320,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
-      <c r="D686" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D686" t="inlineStr"/>
+      <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
         <v>2</v>
       </c>
@@ -16346,14 +16338,18 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
-      <c r="D687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F687" t="n">
@@ -16390,12 +16386,16 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr"/>
-      <c r="E689" t="inlineStr"/>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="F689" t="n">
         <v>2</v>
       </c>
@@ -16470,15 +16470,11 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
-      <c r="D693" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D693" t="inlineStr"/>
       <c r="E693" t="inlineStr"/>
       <c r="F693" t="n">
         <v>3</v>
@@ -16514,11 +16510,15 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr"/>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="n">
         <v>3</v>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16944,18 +16944,22 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>$-114.7B</t>
+        </is>
+      </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F718" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="719">
@@ -16966,18 +16970,14 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr">
+      <c r="D719" t="inlineStr"/>
+      <c r="E719" t="inlineStr">
         <is>
           <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E719" t="inlineStr">
-        <is>
-          <t>0.2%</t>
         </is>
       </c>
       <c r="F719" t="n">
@@ -16992,14 +16992,18 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr"/>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F720" t="n">
@@ -17014,18 +17018,18 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F721" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="722">
@@ -17036,22 +17040,22 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F722" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="723">
@@ -17062,13 +17066,13 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -17088,18 +17092,18 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E724" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="F724" t="n">
@@ -17114,22 +17118,22 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F725" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="726">
@@ -17162,18 +17166,18 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F727" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="728">
@@ -17184,22 +17188,18 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F728" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="729">
@@ -17210,22 +17210,18 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F729" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="730">
@@ -17236,22 +17232,22 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F730" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="731">
@@ -17284,22 +17280,22 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
       <c r="D732" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="F732" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="733">
@@ -17310,18 +17306,22 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
-      <c r="D733" t="inlineStr"/>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F733" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="734">
@@ -17332,18 +17332,22 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
-      <c r="D734" t="inlineStr"/>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F734" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735">
@@ -17354,18 +17358,14 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
-      <c r="D735" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D735" t="inlineStr"/>
       <c r="E735" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F735" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17600,18 +17600,18 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="747">
@@ -17622,14 +17622,14 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F747" t="n">
@@ -17644,18 +17644,18 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F748" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="749">
@@ -17710,18 +17710,18 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="F751" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="752">
@@ -17754,18 +17754,18 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F753" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="754">
@@ -17776,7 +17776,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -18062,14 +18062,14 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
       <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr"/>
       <c r="F769" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="770">
@@ -18080,14 +18080,14 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
       <c r="D770" t="inlineStr"/>
       <c r="E770" t="inlineStr"/>
       <c r="F770" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="771">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -18134,14 +18134,14 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
       <c r="D773" t="inlineStr"/>
       <c r="E773" t="inlineStr"/>
       <c r="F773" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="774">
@@ -18152,7 +18152,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
@@ -18170,14 +18170,14 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
       <c r="D775" t="inlineStr"/>
       <c r="E775" t="inlineStr"/>
       <c r="F775" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="776">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
@@ -18206,7 +18206,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -18286,12 +18286,20 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalFEB</t>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr"/>
-      <c r="E781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="F781" t="n">
         <v>2</v>
       </c>
@@ -18304,20 +18312,12 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalFEB</t>
+          <t>S&amp;P Global Composite PMI FinalFEB</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
-      <c r="D782" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="E782" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+      <c r="D782" t="inlineStr"/>
+      <c r="E782" t="inlineStr"/>
       <c r="F782" t="n">
         <v>2</v>
       </c>
@@ -18378,18 +18378,18 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
       <c r="D785" t="inlineStr"/>
       <c r="E785" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F785" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="786">
@@ -18400,18 +18400,18 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
       <c r="D786" t="inlineStr"/>
       <c r="E786" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F786" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="787">
@@ -18422,14 +18422,14 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C787" t="inlineStr"/>
       <c r="D787" t="inlineStr"/>
       <c r="E787" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F787" t="n">
@@ -18444,14 +18444,14 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
       <c r="D788" t="inlineStr"/>
       <c r="E788" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F788" t="n">
@@ -18466,18 +18466,18 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr"/>
       <c r="E789" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="F789" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="790">
@@ -18488,18 +18488,18 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
       <c r="D790" t="inlineStr"/>
       <c r="E790" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="F790" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="791">
@@ -18532,12 +18532,16 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C792" t="inlineStr"/>
       <c r="D792" t="inlineStr"/>
-      <c r="E792" t="inlineStr"/>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="F792" t="n">
         <v>3</v>
       </c>
@@ -18550,16 +18554,12 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="inlineStr"/>
-      <c r="E793" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
+      <c r="E793" t="inlineStr"/>
       <c r="F793" t="n">
         <v>3</v>
       </c>
@@ -18572,14 +18572,14 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="inlineStr"/>
       <c r="E794" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="F794" t="n">
@@ -18594,14 +18594,14 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C795" t="inlineStr"/>
       <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="F795" t="n">
@@ -18616,14 +18616,14 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C796" t="inlineStr"/>
       <c r="D796" t="inlineStr"/>
       <c r="E796" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="F796" t="n">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
@@ -18754,14 +18754,14 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr"/>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="804">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
@@ -18790,14 +18790,14 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
       <c r="E805" t="inlineStr"/>
       <c r="F805" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="806">
@@ -18808,14 +18808,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="807">
@@ -18839,12 +18839,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2025-03-05 22:00:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
@@ -18857,18 +18857,216 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2025-03-05 22:00:00+05:30</t>
+          <t>2025-03-05 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr"/>
+      <c r="D810" t="inlineStr"/>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr"/>
+      <c r="D811" t="inlineStr"/>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr"/>
+      <c r="D812" t="inlineStr"/>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr"/>
+      <c r="D813" t="inlineStr"/>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr"/>
+      <c r="D814" t="inlineStr"/>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr"/>
+      <c r="D815" t="inlineStr"/>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2025-03-05 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr"/>
+      <c r="D816" t="inlineStr"/>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2025-03-05 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Total Vehicle SalesFEB</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr"/>
+      <c r="D817" t="inlineStr"/>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2025-03-05 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>17-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr"/>
+      <c r="D818" t="inlineStr"/>
+      <c r="E818" t="inlineStr"/>
+      <c r="F818" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2025-03-05 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>17-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr"/>
+      <c r="D819" t="inlineStr"/>
+      <c r="E819" t="inlineStr"/>
+      <c r="F819" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2025-03-05 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Total Vehicle SalesFEB</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr"/>
+      <c r="D820" t="inlineStr"/>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="n">
         <v>3</v>
       </c>
     </row>
